--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.7818591605734</v>
+        <v>3.702052113593178</v>
       </c>
       <c r="D2" t="n">
-        <v>22.70157857792195</v>
+        <v>3.689006518912317</v>
       </c>
       <c r="E2" t="n">
-        <v>12.90375141812673</v>
+        <v>2.096859605445593</v>
       </c>
       <c r="F2" t="n">
-        <v>12.69082762961477</v>
+        <v>2.0622594898124</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9113260379667</v>
+        <v>5.835590481169589</v>
       </c>
       <c r="D3" t="n">
-        <v>35.67886309429171</v>
+        <v>5.797815252822403</v>
       </c>
       <c r="E3" t="n">
-        <v>12.90375141812673</v>
+        <v>2.096859605445593</v>
       </c>
       <c r="F3" t="n">
-        <v>12.69082762961477</v>
+        <v>2.0622594898124</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4469253804053</v>
+        <v>0.7226253743158614</v>
       </c>
       <c r="D4" t="n">
-        <v>4.726992480132151</v>
+        <v>0.7681362780214746</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90375141812673</v>
+        <v>2.096859605445593</v>
       </c>
       <c r="F4" t="n">
-        <v>12.69082762961477</v>
+        <v>2.0622594898124</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
